--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/12_relationships.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/12_relationships.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rcde869251fd945df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rce321eb76de74c52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R33fd3f6f104a4d5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R156b92c690804ac3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R676da49d1eca4f69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R5ee1838c899b4140"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Allowed Relationships" sheetId="7" r:id="R04d3e144c0604958"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R7b95063e95654a59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R34617816897f4fda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R5918b47bbf354af6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rf2571e4bab3c4165"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R0e423b78badd477f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rd87865a0f05b440c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Allowed Relationships" sheetId="7" r:id="R1fe0709d24da41b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -628,7 +628,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e23517777bd4747"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7f09e0a2ada4787"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -749,7 +749,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I6" s="80" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Executive Office Workflow Platform supports Executive Office (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -781,7 +781,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I7" s="81" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Executive Office owned by Chief Strategy Officer (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J7" s="43" t="str">
         <x:v>Medium</x:v>
@@ -813,7 +813,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I8" s="81" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Executive Office Operational Dataset produced by Executive Office Workflow Platform (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J8" s="43" t="str">
         <x:v>Medium</x:v>
@@ -845,7 +845,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I9" s="81" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Executive Office Analytics Mart consumes Executive Office Operational Dataset (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J9" s="43" t="str">
         <x:v>Medium</x:v>
@@ -877,7 +877,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I10" s="81" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Executive Office Workflow Platform feeds Executive Office Analytics Mart (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J10" s="43" t="str">
         <x:v>Medium</x:v>
@@ -909,7 +909,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I11" s="81" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Executive Office Analytics Mart integrates with Executive Office Reporting Workspace (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J11" s="43" t="str">
         <x:v>Medium</x:v>
@@ -941,7 +941,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I12" s="82" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Executive Office Reporting Workspace depends on Executive Office Workflow Platform (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J12" s="45" t="str">
         <x:v>Medium</x:v>
@@ -973,7 +973,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I13" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Executive Office Workflow Platform hosted on Executive Office Primary Northeast Data Center Hosting Segment (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J13" t="str">
         <x:v>Medium</x:v>
@@ -1005,7 +1005,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I14" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Executive Office Workflow Platform hosted in Primary Northeast Data Center (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J14" t="str">
         <x:v>Medium</x:v>
@@ -1037,7 +1037,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I15" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Snowflake / Databricks Cloud Data Platform target for Executive Office Operational Dataset (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J15" t="str">
         <x:v>Medium</x:v>
@@ -1069,7 +1069,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I16" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Executive Office governed by Enterprise Strategy governance council (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J16" t="str">
         <x:v>Medium</x:v>
@@ -1101,7 +1101,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I17" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Enterprise profile and corporate priorities program funded by Chief Strategy Officer (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J17" t="str">
         <x:v>Medium</x:v>
@@ -1133,7 +1133,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I18" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Snowflake / Databricks Cloud Data Platform replaces candidate legacy Executive Office Operational Dataset (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J18" t="str">
         <x:v>Medium</x:v>
@@ -1165,7 +1165,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I19" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Executive Office used by Executive Office Analyst / Steward (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J19" t="str">
         <x:v>Medium</x:v>
@@ -1197,7 +1197,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I20" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Executive Office Operational Dataset part of Enterprise profile and corporate priorities modernization and readiness program (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J20" t="str">
         <x:v>Medium</x:v>
@@ -1229,7 +1229,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I21" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate ServiceNow provides Executive Office Workflow Platform (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J21" t="str">
         <x:v>Medium</x:v>
@@ -1261,7 +1261,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I22" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Executive Office measured by Executive Office cycle time (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J22" t="str">
         <x:v>Medium</x:v>
@@ -1293,7 +1293,7 @@
         <x:v>HARBORTRUST-BANK-HT-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I23" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Executive Office has risk Executive Office data lineage and definition risk (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J23" t="str">
         <x:v>Medium</x:v>
@@ -1325,7 +1325,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I24" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile FIS Core Banking Platform supports Retail Deposits and Branch Operations (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J24" t="str">
         <x:v>Medium</x:v>
@@ -1357,7 +1357,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I25" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Retail Deposits and Branch Operations owned by Retail Banking COO (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J25" t="str">
         <x:v>Medium</x:v>
@@ -1389,7 +1389,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I26" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Retail Deposits Branch Operations Operational Dataset produced by FIS Core Banking Platform (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J26" t="str">
         <x:v>Medium</x:v>
@@ -1421,7 +1421,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I27" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Branch Teller Platform consumes Retail Deposits Branch Operations Operational Dataset (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J27" t="str">
         <x:v>Medium</x:v>
@@ -1453,7 +1453,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I28" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for FIS Core Banking Platform feeds Retail Deposits Branch Operations Analytics Mart (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J28" t="str">
         <x:v>Medium</x:v>
@@ -1485,7 +1485,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I29" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Branch Teller Platform integrates with Digital Banking Servicing Portal (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J29" t="str">
         <x:v>Medium</x:v>
@@ -1517,7 +1517,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I30" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Digital Banking Servicing Portal depends on FIS Core Banking Platform (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J30" t="str">
         <x:v>Medium</x:v>
@@ -1549,7 +1549,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I31" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate FIS Core Banking Platform hosted on Retail Deposits and Branch Operations Primary Northeast Data Center Hosting Segment (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J31" t="str">
         <x:v>Medium</x:v>
@@ -1581,7 +1581,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I32" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm FIS Core Banking Platform hosted in Primary Northeast Data Center (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J32" t="str">
         <x:v>Medium</x:v>
@@ -1613,7 +1613,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I33" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Snowflake / Databricks Cloud Data Platform target for Retail Deposits Branch Operations Operational Dataset (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J33" t="str">
         <x:v>Medium</x:v>
@@ -1645,7 +1645,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I34" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Retail Deposits and Branch Operations governed by Retail Banking governance council (record 29) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J34" t="str">
         <x:v>Medium</x:v>
@@ -1677,7 +1677,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I35" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Retail banking program funded by Retail Banking COO (record 30) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J35" t="str">
         <x:v>Medium</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I36" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Snowflake / Databricks Cloud Data Platform replaces candidate legacy Retail Deposits Branch Operations Operational Dataset (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J36" t="str">
         <x:v>Medium</x:v>
@@ -1741,7 +1741,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I37" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Retail Deposits and Branch Operations used by Retail Deposits and Branch Operations Analyst / Steward (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J37" t="str">
         <x:v>Medium</x:v>
@@ -1773,7 +1773,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I38" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Retail Deposits Branch Operations Operational Dataset part of Retail banking modernization and readiness program (record 33), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J38" t="str">
         <x:v>Medium</x:v>
@@ -1805,7 +1805,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I39" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile FIS provides FIS Core Banking Platform (record 34) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J39" t="str">
         <x:v>Medium</x:v>
@@ -1837,7 +1837,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I40" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Retail Deposits and Branch Operations measured by Retail Deposits and Branch Operations cycle time (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J40" t="str">
         <x:v>Medium</x:v>
@@ -1869,7 +1869,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-EV01</x:v>
       </x:c>
       <x:c r="I41" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Retail Deposits and Branch Operations has risk Retail Deposits and Branch Operations data lineage and definition risk (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J41" t="str">
         <x:v>Medium</x:v>
@@ -1901,7 +1901,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I42" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Commercial Lending and Treasury Workflow Platform supports Commercial Lending and Treasury (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J42" t="str">
         <x:v>Medium</x:v>
@@ -1933,7 +1933,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I43" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Commercial Lending and Treasury owned by Commercial Banking COO (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J43" t="str">
         <x:v>Medium</x:v>
@@ -1965,7 +1965,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I44" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Commercial Lending Treasury Operational Dataset produced by Commercial Lending and Treasury Workflow Platform (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J44" t="str">
         <x:v>Medium</x:v>
@@ -1997,7 +1997,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I45" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Commercial Lending and Treasury Analytics Mart consumes Commercial Lending Treasury Operational Dataset (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J45" t="str">
         <x:v>Medium</x:v>
@@ -2029,7 +2029,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I46" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Commercial Lending and Treasury Workflow Platform feeds Commercial Lending Treasury Analytics Mart (record 41) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J46" t="str">
         <x:v>Medium</x:v>
@@ -2061,7 +2061,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I47" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Commercial Lending and Treasury Analytics Mart integrates with Commercial Lending and Treasury Reporting Workspace (record 42) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J47" t="str">
         <x:v>Medium</x:v>
@@ -2093,7 +2093,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I48" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Commercial Lending and Treasury Reporting Workspace depends on Commercial Lending and Treasury Workflow Platform (record 43), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J48" t="str">
         <x:v>Medium</x:v>
@@ -2125,7 +2125,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I49" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Commercial Lending and Treasury Workflow Platform hosted on Commercial Lending and Treasury Primary Northeast Data Center Hosting Segment (record 44) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J49" t="str">
         <x:v>Medium</x:v>
@@ -2157,7 +2157,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I50" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Commercial Lending and Treasury Workflow Platform hosted in Primary Northeast Data Center (record 45) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J50" t="str">
         <x:v>Medium</x:v>
@@ -2189,7 +2189,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I51" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Snowflake / Databricks Cloud Data Platform target for Commercial Lending Treasury Operational Dataset (record 46) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J51" t="str">
         <x:v>Medium</x:v>
@@ -2221,7 +2221,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I52" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Commercial Lending and Treasury governed by Commercial Banking governance council (record 47) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J52" t="str">
         <x:v>Medium</x:v>
@@ -2253,7 +2253,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I53" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Commercial banking program funded by Commercial Banking COO (record 48), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J53" t="str">
         <x:v>Medium</x:v>
@@ -2285,7 +2285,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I54" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Snowflake / Databricks Cloud Data Platform replaces candidate legacy Commercial Lending Treasury Operational Dataset (record 49) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J54" t="str">
         <x:v>Medium</x:v>
@@ -2317,7 +2317,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I55" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Commercial Lending and Treasury used by Commercial Lending and Treasury Analyst / Steward (record 50) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J55" t="str">
         <x:v>Medium</x:v>
@@ -2349,7 +2349,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I56" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Commercial Lending Treasury Operational Dataset part of Commercial banking modernization and readiness program (record 51) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J56" t="str">
         <x:v>Medium</x:v>
@@ -2381,7 +2381,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I57" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Azure provides Commercial Lending and Treasury Workflow Platform (record 52) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J57" t="str">
         <x:v>Medium</x:v>
@@ -2413,7 +2413,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I58" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Commercial Lending and Treasury measured by Commercial Lending and Treasury cycle time (record 53), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J58" t="str">
         <x:v>Medium</x:v>
@@ -2445,7 +2445,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMMERCIAL-EV01</x:v>
       </x:c>
       <x:c r="I59" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Commercial Lending and Treasury has risk Commercial Lending and Treasury data lineage and definition risk (record 54) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J59" t="str">
         <x:v>Medium</x:v>
@@ -2477,7 +2477,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I60" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Operations Workflow Platform supports Cards Operations (record 55) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J60" t="str">
         <x:v>Medium</x:v>
@@ -2509,7 +2509,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I61" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Cards Operations owned by Head of Cards (record 56) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J61" t="str">
         <x:v>Medium</x:v>
@@ -2541,7 +2541,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I62" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Cards Operations Operational Dataset produced by Cards Operations Workflow Platform (record 57) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J62" t="str">
         <x:v>Medium</x:v>
@@ -2573,7 +2573,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I63" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Cards Operations Analytics Mart consumes Cards Operations Operational Dataset (record 58), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J63" t="str">
         <x:v>Medium</x:v>
@@ -2605,7 +2605,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I64" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Cards Operations Workflow Platform feeds Cards Operations Analytics Mart (record 59) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J64" t="str">
         <x:v>Medium</x:v>
@@ -2637,7 +2637,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I65" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Operations Analytics Mart integrates with Cards Operations Reporting Workspace (record 60) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J65" t="str">
         <x:v>Medium</x:v>
@@ -2669,7 +2669,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I66" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Cards Operations Reporting Workspace depends on Cards Operations Workflow Platform (record 61) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J66" t="str">
         <x:v>Medium</x:v>
@@ -2701,7 +2701,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I67" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Cards Operations Workflow Platform hosted on Cards Operations Primary Northeast Data Center Hosting Segment (record 62) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J67" t="str">
         <x:v>Medium</x:v>
@@ -2733,7 +2733,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I68" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Cards Operations Workflow Platform hosted in Primary Northeast Data Center (record 63), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J68" t="str">
         <x:v>Medium</x:v>
@@ -2765,7 +2765,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I69" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Snowflake / Databricks Cloud Data Platform target for Cards Operations Operational Dataset (record 64) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J69" t="str">
         <x:v>Medium</x:v>
@@ -2797,7 +2797,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I70" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Operations governed by Cards and Consumer Lending governance council (record 65) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J70" t="str">
         <x:v>Medium</x:v>
@@ -2829,7 +2829,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I71" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Cards program funded by Head of Cards (record 66) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J71" t="str">
         <x:v>Medium</x:v>
@@ -2861,7 +2861,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I72" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Snowflake / Databricks Cloud Data Platform replaces candidate legacy Cards Operations Operational Dataset (record 67) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J72" t="str">
         <x:v>Medium</x:v>
@@ -2893,7 +2893,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I73" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Cards Operations used by Cards Operations Analyst / Steward (record 68), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J73" t="str">
         <x:v>Medium</x:v>
@@ -2925,7 +2925,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I74" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Cards Operations Operational Dataset part of Cards modernization and readiness program (record 69) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J74" t="str">
         <x:v>Medium</x:v>
@@ -2957,7 +2957,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I75" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for ServiceNow provides Cards Operations Workflow Platform (record 70) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J75" t="str">
         <x:v>Medium</x:v>
@@ -2989,7 +2989,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I76" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Cards Operations measured by Cards Operations cycle time (record 71) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J76" t="str">
         <x:v>Medium</x:v>
@@ -3021,7 +3021,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-EV01</x:v>
       </x:c>
       <x:c r="I77" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Cards Operations has risk Cards Operations data lineage and definition risk (record 72) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J77" t="str">
         <x:v>Medium</x:v>
@@ -3053,7 +3053,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I78" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Payments Hub supports Payments Operations (record 73), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J78" t="str">
         <x:v>Medium</x:v>
@@ -3085,7 +3085,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I79" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Payments Operations owned by Payments Leader (record 74) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J79" t="str">
         <x:v>Medium</x:v>
@@ -3117,7 +3117,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I80" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments Operations Operational Dataset produced by Payments Hub (record 75) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J80" t="str">
         <x:v>Medium</x:v>
@@ -3149,7 +3149,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I81" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate ACH Wire Gateway consumes Payments Operations Operational Dataset (record 76) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J81" t="str">
         <x:v>Medium</x:v>
@@ -3181,7 +3181,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I82" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Payments Hub feeds Payments Operations Analytics Mart (record 77) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J82" t="str">
         <x:v>Medium</x:v>
@@ -3213,7 +3213,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I83" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for ACH Wire Gateway integrates with Real-Time Payments Adapter (record 78), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J83" t="str">
         <x:v>Medium</x:v>
@@ -3245,7 +3245,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I84" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Real-Time Payments Adapter depends on Payments Hub (record 79) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J84" t="str">
         <x:v>Medium</x:v>
@@ -3277,7 +3277,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I85" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments Hub hosted on Payments Operations Primary Northeast Data Center Hosting Segment (record 80) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J85" t="str">
         <x:v>Medium</x:v>
@@ -3309,7 +3309,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I86" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Payments Hub hosted in Primary Northeast Data Center (record 81) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J86" t="str">
         <x:v>Medium</x:v>
@@ -3341,7 +3341,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I87" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Snowflake / Databricks Cloud Data Platform target for Payments Operations Operational Dataset (record 82) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J87" t="str">
         <x:v>Medium</x:v>
@@ -3373,7 +3373,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I88" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Payments Operations governed by Payments governance council (record 83), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J88" t="str">
         <x:v>Medium</x:v>
@@ -3405,7 +3405,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I89" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Payments program funded by Payments Leader (record 84) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J89" t="str">
         <x:v>Medium</x:v>
@@ -3437,7 +3437,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I90" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Snowflake / Databricks Cloud Data Platform replaces candidate legacy Payments Operations Operational Dataset (record 85) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J90" t="str">
         <x:v>Medium</x:v>
@@ -3469,7 +3469,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I91" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Payments Operations used by Payments Operations Analyst / Steward (record 86) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J91" t="str">
         <x:v>Medium</x:v>
@@ -3501,7 +3501,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I92" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Payments Operations Operational Dataset part of Payments modernization and readiness program (record 87) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J92" t="str">
         <x:v>Medium</x:v>
@@ -3533,7 +3533,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I93" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Informatica provides Payments Hub (record 88), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J93" t="str">
         <x:v>Medium</x:v>
@@ -3565,7 +3565,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I94" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Payments Operations measured by Payments Operations cycle time (record 89) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J94" t="str">
         <x:v>Medium</x:v>
@@ -3597,7 +3597,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-EV01</x:v>
       </x:c>
       <x:c r="I95" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments Operations has risk Payments Operations data lineage and definition risk (record 90) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J95" t="str">
         <x:v>Medium</x:v>
@@ -3629,7 +3629,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I96" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Consumer Lending Operations Workflow Platform supports Consumer Lending Operations (record 91) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J96" t="str">
         <x:v>Medium</x:v>
@@ -3661,7 +3661,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I97" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Consumer Lending Operations owned by Head of Consumer Lending (record 92) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J97" t="str">
         <x:v>Medium</x:v>
@@ -3693,7 +3693,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I98" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Consumer Lending Operations Operational Dataset produced by Consumer Lending Operations Workflow Platform (record 93), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J98" t="str">
         <x:v>Medium</x:v>
@@ -3725,7 +3725,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I99" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Consumer Lending Operations Analytics Mart consumes Consumer Lending Operations Operational Dataset (record 94) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J99" t="str">
         <x:v>Medium</x:v>
@@ -3757,7 +3757,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I100" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Consumer Lending Operations Workflow Platform feeds Consumer Lending Operations Analytics Mart (record 95) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J100" t="str">
         <x:v>Medium</x:v>
@@ -3789,7 +3789,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I101" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Consumer Lending Operations Analytics Mart integrates with Consumer Lending Operations Reporting Workspace (record 96) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J101" t="str">
         <x:v>Medium</x:v>
@@ -3821,7 +3821,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I102" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Consumer Lending Operations Reporting Workspace depends on Consumer Lending Operations Workflow Platform (record 97) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J102" t="str">
         <x:v>Medium</x:v>
@@ -3853,7 +3853,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I103" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Consumer Lending Operations Workflow Platform hosted on Consumer Lending Operations Primary Northeast Data Center Hosting Segment (record 98), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J103" t="str">
         <x:v>Medium</x:v>
@@ -3885,7 +3885,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I104" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Consumer Lending Operations Workflow Platform hosted in Primary Northeast Data Center (record 99) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J104" t="str">
         <x:v>Medium</x:v>
@@ -3917,7 +3917,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I105" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Snowflake / Databricks Cloud Data Platform target for Consumer Lending Operations Operational Dataset (record 100) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J105" t="str">
         <x:v>Medium</x:v>
@@ -3949,7 +3949,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I106" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Consumer Lending Operations governed by Consumer Lending governance council (record 101) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J106" t="str">
         <x:v>Medium</x:v>
@@ -3981,7 +3981,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I107" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Lending program funded by Head of Consumer Lending (record 102) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J107" t="str">
         <x:v>Medium</x:v>
@@ -4013,7 +4013,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I108" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Snowflake / Databricks Cloud Data Platform replaces candidate legacy Consumer Lending Operations Operational Dataset (record 103), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J108" t="str">
         <x:v>Medium</x:v>
@@ -4045,7 +4045,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I109" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Consumer Lending Operations used by Consumer Lending Operations Analyst / Steward (record 104) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J109" t="str">
         <x:v>Medium</x:v>
@@ -4077,7 +4077,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I110" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Consumer Lending Operations Operational Dataset part of Lending modernization and readiness program (record 105) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J110" t="str">
         <x:v>Medium</x:v>
@@ -4109,7 +4109,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I111" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate NICE provides Consumer Lending Operations Workflow Platform (record 106) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J111" t="str">
         <x:v>Medium</x:v>
@@ -4141,7 +4141,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I112" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Consumer Lending Operations measured by Consumer Lending Operations cycle time (record 107) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J112" t="str">
         <x:v>Medium</x:v>
@@ -4173,7 +4173,7 @@
         <x:v>HARBORTRUST-BANK-HT-LENDING-EV01</x:v>
       </x:c>
       <x:c r="I113" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Consumer Lending Operations has risk Consumer Lending Operations data lineage and definition risk (record 108), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J113" t="str">
         <x:v>Medium</x:v>
@@ -4205,7 +4205,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I114" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Wealth Advisory and Brokerage Workflow Platform supports Wealth Advisory and Brokerage (record 109) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J114" t="str">
         <x:v>Medium</x:v>
@@ -4237,7 +4237,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I115" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Wealth Advisory and Brokerage owned by Head of Wealth (record 110) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J115" t="str">
         <x:v>Medium</x:v>
@@ -4269,7 +4269,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I116" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Wealth Advisory Brokerage Operational Dataset produced by Wealth Advisory and Brokerage Workflow Platform (record 111) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J116" t="str">
         <x:v>Medium</x:v>
@@ -4301,7 +4301,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I117" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Wealth Advisory and Brokerage Analytics Mart consumes Wealth Advisory Brokerage Operational Dataset (record 112) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J117" t="str">
         <x:v>Medium</x:v>
@@ -4333,7 +4333,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I118" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Wealth Advisory and Brokerage Workflow Platform feeds Wealth Advisory Brokerage Analytics Mart (record 113), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J118" t="str">
         <x:v>Medium</x:v>
@@ -4365,7 +4365,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I119" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Wealth Advisory and Brokerage Analytics Mart integrates with Wealth Advisory and Brokerage Reporting Workspace (record 114) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J119" t="str">
         <x:v>Medium</x:v>
@@ -4397,7 +4397,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I120" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Wealth Advisory and Brokerage Reporting Workspace depends on Wealth Advisory and Brokerage Workflow Platform (record 115) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J120" t="str">
         <x:v>Medium</x:v>
@@ -4429,7 +4429,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I121" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Wealth Advisory and Brokerage Workflow Platform hosted on Wealth Advisory and Brokerage Primary Northeast Data Center Hosting Segment (record 116) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J121" t="str">
         <x:v>Medium</x:v>
@@ -4461,7 +4461,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I122" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Wealth Advisory and Brokerage Workflow Platform hosted in Primary Northeast Data Center (record 117) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J122" t="str">
         <x:v>Medium</x:v>
@@ -4493,7 +4493,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I123" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Snowflake / Databricks Cloud Data Platform target for Wealth Advisory Brokerage Operational Dataset (record 118), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J123" t="str">
         <x:v>Medium</x:v>
@@ -4525,7 +4525,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I124" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Wealth Advisory and Brokerage governed by Wealth Management governance council (record 119) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J124" t="str">
         <x:v>Medium</x:v>
@@ -4557,7 +4557,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I125" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Wealth program funded by Head of Wealth (record 120) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J125" t="str">
         <x:v>Medium</x:v>
@@ -4589,7 +4589,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I126" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Snowflake / Databricks Cloud Data Platform replaces candidate legacy Wealth Advisory Brokerage Operational Dataset (record 121) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J126" t="str">
         <x:v>Medium</x:v>
@@ -4621,7 +4621,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I127" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Wealth Advisory and Brokerage used by Wealth Advisory and Brokerage Analyst / Steward (record 122) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J127" t="str">
         <x:v>Medium</x:v>
@@ -4653,7 +4653,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I128" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Wealth Advisory Brokerage Operational Dataset part of Wealth modernization and readiness program (record 123), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J128" t="str">
         <x:v>Medium</x:v>
@@ -4685,7 +4685,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I129" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile ServiceNow provides Wealth Advisory and Brokerage Workflow Platform (record 124) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J129" t="str">
         <x:v>Medium</x:v>
@@ -4717,7 +4717,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I130" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Wealth Advisory and Brokerage measured by Wealth Advisory and Brokerage cycle time (record 125) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J130" t="str">
         <x:v>Medium</x:v>
@@ -4749,7 +4749,7 @@
         <x:v>HARBORTRUST-BANK-HT-WEALTH-EV01</x:v>
       </x:c>
       <x:c r="I131" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Wealth Advisory and Brokerage has risk Wealth Advisory and Brokerage data lineage and definition risk (record 126) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J131" t="str">
         <x:v>Medium</x:v>
@@ -4775,13 +4775,13 @@
         <x:v>Business Function</x:v>
       </x:c>
       <x:c r="G132" t="str">
-        <x:v>Fraud Alert Platform supports fraud alerts, case triage, AML/transaction monitoring, loss prevention.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: The fraud alert platform captures model score and reason codes, but downstream case outcomes are not consistently fed back to the feature store.</x:v>
       </x:c>
       <x:c r="H132" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.</x:v>
       </x:c>
       <x:c r="I132" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud Alert Platform supports Fraud and Risk Operations (record 127) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J132" t="str">
         <x:v>Medium</x:v>
@@ -4807,13 +4807,13 @@
         <x:v>Owner / Executive Role</x:v>
       </x:c>
       <x:c r="G133" t="str">
-        <x:v>CRO is accountable for Fraud and Risk Operations evidence and readiness.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: AML transaction monitoring and real-time fraud decisions use overlapping customer and counterparty fields with different freshness rules.</x:v>
       </x:c>
       <x:c r="H133" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>AML transaction monitoring source inventory and control-owner interview.</x:v>
       </x:c>
       <x:c r="I133" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Operations owned by CRO (record 128) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J133" t="str">
         <x:v>Medium</x:v>
@@ -4839,13 +4839,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G134" t="str">
-        <x:v>Fraud Risk Operations Operational Dataset is produced or sourced from Fraud Alert Platform.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: High-risk digital onboarding cases require manual lookup across KYC vendor evidence, device intelligence, and core banking account history.</x:v>
       </x:c>
       <x:c r="H134" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Digital onboarding/KYC vendor report with identity verification and device-risk signals.</x:v>
       </x:c>
       <x:c r="I134" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud Risk Operations Operational Dataset produced by Fraud Alert Platform (record 129) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J134" t="str">
         <x:v>Medium</x:v>
@@ -4871,13 +4871,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G135" t="str">
-        <x:v>AML Transaction Monitoring consumes Fraud Risk Operations Operational Dataset for analytics/workflow support.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Operations leaders cannot separate true model drift from queue staffing backlogs without alert age, model version, analyst action, and loss outcome in one view.</x:v>
       </x:c>
       <x:c r="H135" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Fraud feature store design notes with feedback-loop and model governance gaps.</x:v>
       </x:c>
       <x:c r="I135" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate AML Transaction Monitoring consumes Fraud Risk Operations Operational Dataset (record 130) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J135" t="str">
         <x:v>Medium</x:v>
@@ -4903,13 +4903,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G136" t="str">
-        <x:v>Fraud Alert Platform feeds Fraud Risk Operations Analytics Mart through batch/API/interface flows that require lineage validation.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Fraud analysts triage card, ACH, wire, digital-login, and mule-account alerts in separate queues with inconsistent case priority rules.</x:v>
       </x:c>
       <x:c r="H136" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.</x:v>
       </x:c>
       <x:c r="I136" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud Alert Platform feeds Fraud Risk Operations Analytics Mart (record 131) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J136" t="str">
         <x:v>Medium</x:v>
@@ -4935,13 +4935,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G137" t="str">
-        <x:v>AML Transaction Monitoring integrates with Fraud Case Management for workflow, reporting, or exception handling.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: The fraud alert platform captures model score and reason codes, but downstream case outcomes are not consistently fed back to the feature store.</x:v>
       </x:c>
       <x:c r="H137" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.</x:v>
       </x:c>
       <x:c r="I137" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate AML Transaction Monitoring integrates with Fraud Case Management (record 132) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J137" t="str">
         <x:v>Medium</x:v>
@@ -4967,13 +4967,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G138" t="str">
-        <x:v>Fraud Case Management depends on Fraud Alert Platform for source data, workflow handoff, or identity/transaction context.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: AML transaction monitoring and real-time fraud decisions use overlapping customer and counterparty fields with different freshness rules.</x:v>
       </x:c>
       <x:c r="H138" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>AML transaction monitoring source inventory and control-owner interview.</x:v>
       </x:c>
       <x:c r="I138" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud Case Management depends on Fraud Alert Platform (record 133) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J138" t="str">
         <x:v>Medium</x:v>
@@ -4999,13 +4999,13 @@
         <x:v>Infrastructure / Platform</x:v>
       </x:c>
       <x:c r="G139" t="str">
-        <x:v>Fraud Alert Platform is hosted on or materially depends on the Fraud and Risk Operations hosting segment.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: High-risk digital onboarding cases require manual lookup across KYC vendor evidence, device intelligence, and core banking account history.</x:v>
       </x:c>
       <x:c r="H139" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Digital onboarding/KYC vendor report with identity verification and device-risk signals.</x:v>
       </x:c>
       <x:c r="I139" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud Alert Platform hosted on Fraud and Risk Operations Primary Northeast Data Center Hosting Segment (record 134) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J139" t="str">
         <x:v>Medium</x:v>
@@ -5031,13 +5031,13 @@
         <x:v>Infrastructure / Platform</x:v>
       </x:c>
       <x:c r="G140" t="str">
-        <x:v>Fraud Alert Platform has current or dependent hosting in Primary Northeast Data Center.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Operations leaders cannot separate true model drift from queue staffing backlogs without alert age, model version, analyst action, and loss outcome in one view.</x:v>
       </x:c>
       <x:c r="H140" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Fraud feature store design notes with feedback-loop and model governance gaps.</x:v>
       </x:c>
       <x:c r="I140" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud Alert Platform hosted in Primary Northeast Data Center (record 135) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J140" t="str">
         <x:v>Medium</x:v>
@@ -5063,13 +5063,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G141" t="str">
-        <x:v>Snowflake / Databricks Cloud Data Platform is the target path for governed modernization of Fraud Risk Operations Operational Dataset.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Fraud analysts triage card, ACH, wire, digital-login, and mule-account alerts in separate queues with inconsistent case priority rules.</x:v>
       </x:c>
       <x:c r="H141" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.</x:v>
       </x:c>
       <x:c r="I141" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Snowflake / Databricks Cloud Data Platform target for Fraud Risk Operations Operational Dataset (record 136) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J141" t="str">
         <x:v>Medium</x:v>
@@ -5095,13 +5095,13 @@
         <x:v>Governance Forum</x:v>
       </x:c>
       <x:c r="G142" t="str">
-        <x:v>Enterprise Risk governance council should validate evidence, exceptions, metrics, and promotion readiness.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: The fraud alert platform captures model score and reason codes, but downstream case outcomes are not consistently fed back to the feature store.</x:v>
       </x:c>
       <x:c r="H142" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.</x:v>
       </x:c>
       <x:c r="I142" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Operations governed by Enterprise Risk governance council (record 137) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J142" t="str">
         <x:v>Medium</x:v>
@@ -5127,13 +5127,13 @@
         <x:v>Owner / Executive Role</x:v>
       </x:c>
       <x:c r="G143" t="str">
-        <x:v>CRO sponsors or funds the Fraud / risk modernization and readiness program.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: AML transaction monitoring and real-time fraud decisions use overlapping customer and counterparty fields with different freshness rules.</x:v>
       </x:c>
       <x:c r="H143" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>AML transaction monitoring source inventory and control-owner interview.</x:v>
       </x:c>
       <x:c r="I143" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud / risk program funded by CRO (record 138) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J143" t="str">
         <x:v>Medium</x:v>
@@ -5159,13 +5159,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G144" t="str">
-        <x:v>Fraud Risk Operations Operational Dataset is a candidate legacy/fragmented asset to be rationalized or certified through Snowflake / Databricks Cloud Data Platform.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: High-risk digital onboarding cases require manual lookup across KYC vendor evidence, device intelligence, and core banking account history.</x:v>
       </x:c>
       <x:c r="H144" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Digital onboarding/KYC vendor report with identity verification and device-risk signals.</x:v>
       </x:c>
       <x:c r="I144" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Snowflake / Databricks Cloud Data Platform replaces candidate legacy Fraud Risk Operations Operational Dataset (record 139) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J144" t="str">
         <x:v>Medium</x:v>
@@ -5191,13 +5191,13 @@
         <x:v>Workforce Role</x:v>
       </x:c>
       <x:c r="G145" t="str">
-        <x:v>Fraud and Risk Operations analysts and stewards use this context for reporting, reconciliation, and readiness checks.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Operations leaders cannot separate true model drift from queue staffing backlogs without alert age, model version, analyst action, and loss outcome in one view.</x:v>
       </x:c>
       <x:c r="H145" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Fraud feature store design notes with feedback-loop and model governance gaps.</x:v>
       </x:c>
       <x:c r="I145" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Operations used by Fraud and Risk Operations Analyst / Steward (record 140) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J145" t="str">
         <x:v>Medium</x:v>
@@ -5223,13 +5223,13 @@
         <x:v>Program / Initiative</x:v>
       </x:c>
       <x:c r="G146" t="str">
-        <x:v>Fraud Risk Operations Operational Dataset is in scope for Fraud / risk modernization, validation, or context-readiness work.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Fraud analysts triage card, ACH, wire, digital-login, and mule-account alerts in separate queues with inconsistent case priority rules.</x:v>
       </x:c>
       <x:c r="H146" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.</x:v>
       </x:c>
       <x:c r="I146" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud Risk Operations Operational Dataset part of Fraud / risk modernization and readiness program (record 141) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J146" t="str">
         <x:v>Medium</x:v>
@@ -5255,13 +5255,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G147" t="str">
-        <x:v>Experian provides, supports, or contracts around Fraud Alert Platform.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: The fraud alert platform captures model score and reason codes, but downstream case outcomes are not consistently fed back to the feature store.</x:v>
       </x:c>
       <x:c r="H147" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.</x:v>
       </x:c>
       <x:c r="I147" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Experian provides Fraud Alert Platform (record 142) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J147" t="str">
         <x:v>Medium</x:v>
@@ -5287,13 +5287,13 @@
         <x:v>Metric / Outcome</x:v>
       </x:c>
       <x:c r="G148" t="str">
-        <x:v>Fraud and Risk Operations cycle time measures Fraud and Risk Operations performance.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: AML transaction monitoring and real-time fraud decisions use overlapping customer and counterparty fields with different freshness rules.</x:v>
       </x:c>
       <x:c r="H148" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>AML transaction monitoring source inventory and control-owner interview.</x:v>
       </x:c>
       <x:c r="I148" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Operations measured by Fraud and Risk Operations cycle time (record 143) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J148" t="str">
         <x:v>Medium</x:v>
@@ -5319,13 +5319,13 @@
         <x:v>Risk / Control</x:v>
       </x:c>
       <x:c r="G149" t="str">
-        <x:v>Fraud and Risk Operations has a known evidence/lineage risk until validation is complete.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: High-risk digital onboarding cases require manual lookup across KYC vendor evidence, device intelligence, and core banking account history.</x:v>
       </x:c>
       <x:c r="H149" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-RISK-EV01</x:v>
+        <x:v>Digital onboarding/KYC vendor report with identity verification and device-risk signals.</x:v>
       </x:c>
       <x:c r="I149" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Operations has risk Fraud and Risk Operations data lineage and definition risk (record 144) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J149" t="str">
         <x:v>Medium</x:v>
@@ -5357,7 +5357,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I150" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Compliance and Model Risk Management Workflow Platform supports Compliance and Model Risk Management (record 145) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J150" t="str">
         <x:v>Medium</x:v>
@@ -5389,7 +5389,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I151" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Compliance and Model Risk Management owned by Chief Compliance Officer (record 146) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J151" t="str">
         <x:v>Medium</x:v>
@@ -5421,7 +5421,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I152" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Compliance Model Risk Management Operational Dataset produced by Compliance and Model Risk Management Workflow Platform (record 147) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J152" t="str">
         <x:v>Medium</x:v>
@@ -5453,7 +5453,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I153" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Compliance and Model Risk Management Analytics Mart consumes Compliance Model Risk Management Operational Dataset (record 148), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J153" t="str">
         <x:v>Medium</x:v>
@@ -5485,7 +5485,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I154" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Compliance and Model Risk Management Workflow Platform feeds Compliance Model Risk Management Analytics Mart (record 149) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J154" t="str">
         <x:v>Medium</x:v>
@@ -5517,7 +5517,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I155" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Compliance and Model Risk Management Analytics Mart integrates with Compliance and Model Risk Management Reporting Workspace (record 150) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J155" t="str">
         <x:v>Medium</x:v>
@@ -5549,7 +5549,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I156" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Compliance and Model Risk Management Reporting Workspace depends on Compliance and Model Risk Management Workflow Platform (record 151) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J156" t="str">
         <x:v>Medium</x:v>
@@ -5581,7 +5581,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I157" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Compliance and Model Risk Management Workflow Platform hosted on Compliance and Model Risk Management Primary Northeast Data Center Hosting Segment (record 152) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J157" t="str">
         <x:v>Medium</x:v>
@@ -5613,7 +5613,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I158" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Compliance and Model Risk Management Workflow Platform hosted in Primary Northeast Data Center (record 153), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J158" t="str">
         <x:v>Medium</x:v>
@@ -5645,7 +5645,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I159" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Snowflake / Databricks Cloud Data Platform target for Compliance Model Risk Management Operational Dataset (record 154) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J159" t="str">
         <x:v>Medium</x:v>
@@ -5677,7 +5677,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I160" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Compliance and Model Risk Management governed by Compliance and Model Risk governance council (record 155) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J160" t="str">
         <x:v>Medium</x:v>
@@ -5709,7 +5709,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I161" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Compliance / model risk program funded by Chief Compliance Officer (record 156) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J161" t="str">
         <x:v>Medium</x:v>
@@ -5741,7 +5741,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I162" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Snowflake / Databricks Cloud Data Platform replaces candidate legacy Compliance Model Risk Management Operational Dataset (record 157) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J162" t="str">
         <x:v>Medium</x:v>
@@ -5773,7 +5773,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I163" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Compliance and Model Risk Management used by Compliance and Model Risk Management Analyst / Steward (record 158), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J163" t="str">
         <x:v>Medium</x:v>
@@ -5805,7 +5805,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I164" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Compliance Model Risk Management Operational Dataset part of Compliance / model risk modernization and readiness program (record 159) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J164" t="str">
         <x:v>Medium</x:v>
@@ -5837,7 +5837,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I165" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Databricks provides Compliance and Model Risk Management Workflow Platform (record 160) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J165" t="str">
         <x:v>Medium</x:v>
@@ -5869,7 +5869,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I166" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Compliance and Model Risk Management measured by Compliance and Model Risk Management cycle time (record 161) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J166" t="str">
         <x:v>Medium</x:v>
@@ -5901,7 +5901,7 @@
         <x:v>HARBORTRUST-BANK-HT-COMPLIANCE-EV01</x:v>
       </x:c>
       <x:c r="I167" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Compliance and Model Risk Management has risk Compliance and Model Risk Management data lineage and definition risk (record 162) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J167" t="str">
         <x:v>Medium</x:v>
@@ -5933,7 +5933,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I168" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Contact Center and Servicing Workflow Platform supports Contact Center and Servicing (record 163), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J168" t="str">
         <x:v>Medium</x:v>
@@ -5965,7 +5965,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I169" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Contact Center and Servicing owned by Chief Experience Officer (record 164) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J169" t="str">
         <x:v>Medium</x:v>
@@ -5997,7 +5997,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I170" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact Center Servicing Operational Dataset produced by Contact Center and Servicing Workflow Platform (record 165) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J170" t="str">
         <x:v>Medium</x:v>
@@ -6029,7 +6029,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I171" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Contact Center and Servicing Analytics Mart consumes Contact Center Servicing Operational Dataset (record 166) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J171" t="str">
         <x:v>Medium</x:v>
@@ -6061,7 +6061,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I172" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Contact Center and Servicing Workflow Platform feeds Contact Center Servicing Analytics Mart (record 167) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J172" t="str">
         <x:v>Medium</x:v>
@@ -6093,7 +6093,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I173" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Contact Center and Servicing Analytics Mart integrates with Contact Center and Servicing Reporting Workspace (record 168), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J173" t="str">
         <x:v>Medium</x:v>
@@ -6125,7 +6125,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I174" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Contact Center and Servicing Reporting Workspace depends on Contact Center and Servicing Workflow Platform (record 169) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J174" t="str">
         <x:v>Medium</x:v>
@@ -6157,7 +6157,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I175" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact Center and Servicing Workflow Platform hosted on Contact Center and Servicing Primary Northeast Data Center Hosting Segment (record 170) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J175" t="str">
         <x:v>Medium</x:v>
@@ -6189,7 +6189,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I176" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Contact Center and Servicing Workflow Platform hosted in Primary Northeast Data Center (record 171) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J176" t="str">
         <x:v>Medium</x:v>
@@ -6221,7 +6221,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I177" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Snowflake / Databricks Cloud Data Platform target for Contact Center Servicing Operational Dataset (record 172) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J177" t="str">
         <x:v>Medium</x:v>
@@ -6253,7 +6253,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I178" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Contact Center and Servicing governed by Customer Experience governance council (record 173), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J178" t="str">
         <x:v>Medium</x:v>
@@ -6285,7 +6285,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I179" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Contact center program funded by Chief Experience Officer (record 174) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J179" t="str">
         <x:v>Medium</x:v>
@@ -6317,7 +6317,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I180" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Snowflake / Databricks Cloud Data Platform replaces candidate legacy Contact Center Servicing Operational Dataset (record 175) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J180" t="str">
         <x:v>Medium</x:v>
@@ -6349,7 +6349,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I181" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Contact Center and Servicing used by Contact Center and Servicing Analyst / Steward (record 176) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J181" t="str">
         <x:v>Medium</x:v>
@@ -6381,7 +6381,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I182" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Contact Center Servicing Operational Dataset part of Contact center modernization and readiness program (record 177) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J182" t="str">
         <x:v>Medium</x:v>
@@ -6413,7 +6413,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I183" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Salesforce provides Contact Center and Servicing Workflow Platform (record 178), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J183" t="str">
         <x:v>Medium</x:v>
@@ -6445,7 +6445,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I184" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Contact Center and Servicing measured by Contact Center and Servicing cycle time (record 179) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J184" t="str">
         <x:v>Medium</x:v>
@@ -6477,7 +6477,7 @@
         <x:v>HARBORTRUST-BANK-HT-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I185" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact Center and Servicing has risk Contact Center and Servicing data lineage and definition risk (record 180) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J185" t="str">
         <x:v>Medium</x:v>
@@ -6509,7 +6509,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I186" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Digital Account Opening Platform supports Digital Account Opening and Onboarding (record 181) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J186" t="str">
         <x:v>Medium</x:v>
@@ -6541,7 +6541,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I187" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Digital Account Opening and Onboarding owned by Digital Banking Product Owner (record 182) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J187" t="str">
         <x:v>Medium</x:v>
@@ -6573,7 +6573,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I188" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Digital Account Opening Onboarding Operational Dataset produced by Digital Account Opening Platform (record 183), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J188" t="str">
         <x:v>Medium</x:v>
@@ -6605,7 +6605,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I189" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile KYC Identity Verification Service consumes Digital Account Opening Onboarding Operational Dataset (record 184) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J189" t="str">
         <x:v>Medium</x:v>
@@ -6637,7 +6637,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I190" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Digital Account Opening Platform feeds Digital Account Opening Onboarding Analytics Mart (record 185) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J190" t="str">
         <x:v>Medium</x:v>
@@ -6669,7 +6669,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I191" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate KYC Identity Verification Service integrates with Funding and Account Setup API (record 186) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J191" t="str">
         <x:v>Medium</x:v>
@@ -6701,7 +6701,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I192" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Funding and Account Setup API depends on Digital Account Opening Platform (record 187) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J192" t="str">
         <x:v>Medium</x:v>
@@ -6733,7 +6733,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I193" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Digital Account Opening Platform hosted on Digital Account Opening and Onboarding Primary Northeast Data Center Hosting Segment (record 188), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J193" t="str">
         <x:v>Medium</x:v>
@@ -6765,7 +6765,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I194" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Digital Account Opening Platform hosted in Primary Northeast Data Center (record 189) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J194" t="str">
         <x:v>Medium</x:v>
@@ -6797,7 +6797,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I195" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Snowflake / Databricks Cloud Data Platform target for Digital Account Opening Onboarding Operational Dataset (record 190) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J195" t="str">
         <x:v>Medium</x:v>
@@ -6829,7 +6829,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I196" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Digital Account Opening and Onboarding governed by Digital Banking governance council (record 191) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J196" t="str">
         <x:v>Medium</x:v>
@@ -6861,7 +6861,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I197" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Digital onboarding program funded by Digital Banking Product Owner (record 192) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J197" t="str">
         <x:v>Medium</x:v>
@@ -6893,7 +6893,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I198" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Snowflake / Databricks Cloud Data Platform replaces candidate legacy Digital Account Opening Onboarding Operational Dataset (record 193), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J198" t="str">
         <x:v>Medium</x:v>
@@ -6925,7 +6925,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I199" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Digital Account Opening and Onboarding used by Digital Account Opening and Onboarding Analyst / Steward (record 194) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J199" t="str">
         <x:v>Medium</x:v>
@@ -6957,7 +6957,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I200" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Digital Account Opening Onboarding Operational Dataset part of Digital onboarding modernization and readiness program (record 195) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J200" t="str">
         <x:v>Medium</x:v>
@@ -6989,7 +6989,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I201" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Accenture Managed Services provides Digital Account Opening Platform (record 196) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J201" t="str">
         <x:v>Medium</x:v>
@@ -7021,7 +7021,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I202" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Digital Account Opening and Onboarding measured by Digital Account Opening and Onboarding cycle time (record 197) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J202" t="str">
         <x:v>Medium</x:v>
@@ -7053,7 +7053,7 @@
         <x:v>HARBORTRUST-BANK-HT-DIGITAL-ONBOARDING-EV01</x:v>
       </x:c>
       <x:c r="I203" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Digital Account Opening and Onboarding has risk Digital Account Opening and Onboarding data lineage and definition risk (record 198), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J203" t="str">
         <x:v>Medium</x:v>
@@ -7085,7 +7085,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I204" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile FIS Core Banking Platform supports Core Banking Modernization (record 199) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J204" t="str">
         <x:v>Medium</x:v>
@@ -7117,7 +7117,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I205" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Core Banking Modernization owned by CIO (record 200) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J205" t="str">
         <x:v>Medium</x:v>
@@ -7149,7 +7149,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I206" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Core Banking Modernization Operational Dataset produced by FIS Core Banking Platform (record 201) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J206" t="str">
         <x:v>Medium</x:v>
@@ -7181,7 +7181,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I207" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm IBM z/OS Core Banking Mainframe consumes Core Banking Modernization Operational Dataset (record 202) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J207" t="str">
         <x:v>Medium</x:v>
@@ -7213,7 +7213,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I208" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for FIS Core Banking Platform feeds Core Banking Modernization Analytics Mart (record 203), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J208" t="str">
         <x:v>Medium</x:v>
@@ -7245,7 +7245,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I209" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile IBM z/OS Core Banking Mainframe integrates with Core Banking API Gateway (record 204) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J209" t="str">
         <x:v>Medium</x:v>
@@ -7277,7 +7277,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I210" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Core Banking API Gateway depends on FIS Core Banking Platform (record 205) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J210" t="str">
         <x:v>Medium</x:v>
@@ -7309,7 +7309,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I211" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate FIS Core Banking Platform hosted on Core Banking Modernization Primary Northeast Data Center Hosting Segment (record 206) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J211" t="str">
         <x:v>Medium</x:v>
@@ -7341,7 +7341,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I212" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm FIS Core Banking Platform hosted in Primary Northeast Data Center (record 207) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J212" t="str">
         <x:v>Medium</x:v>
@@ -7373,7 +7373,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I213" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Snowflake / Databricks Cloud Data Platform target for Core Banking Modernization Operational Dataset (record 208), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J213" t="str">
         <x:v>Medium</x:v>
@@ -7405,7 +7405,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I214" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Core Banking Modernization governed by Technology Modernization governance council (record 209) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J214" t="str">
         <x:v>Medium</x:v>
@@ -7437,7 +7437,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I215" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Core banking modernization program funded by CIO (record 210) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J215" t="str">
         <x:v>Medium</x:v>
@@ -7469,7 +7469,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I216" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Snowflake / Databricks Cloud Data Platform replaces candidate legacy Core Banking Modernization Operational Dataset (record 211) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J216" t="str">
         <x:v>Medium</x:v>
@@ -7501,7 +7501,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I217" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Core Banking Modernization used by Core Banking Modernization Analyst / Steward (record 212) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J217" t="str">
         <x:v>Medium</x:v>
@@ -7533,7 +7533,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I218" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Core Banking Modernization Operational Dataset part of Core banking modernization modernization and readiness program (record 213), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J218" t="str">
         <x:v>Medium</x:v>
@@ -7565,7 +7565,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I219" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Databricks provides FIS Core Banking Platform (record 214) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J219" t="str">
         <x:v>Medium</x:v>
@@ -7597,7 +7597,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I220" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Core Banking Modernization measured by Core Banking Modernization cycle time (record 215) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J220" t="str">
         <x:v>Medium</x:v>
@@ -7629,7 +7629,7 @@
         <x:v>HARBORTRUST-BANK-HT-CORE-MODERNIZATION-EV01</x:v>
       </x:c>
       <x:c r="I221" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Core Banking Modernization has risk Core Banking Modernization data lineage and definition risk (record 216) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J221" t="str">
         <x:v>Medium</x:v>
@@ -7661,7 +7661,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I222" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Customer 360 Data Product supports Customer 360 Data Product (record 217) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J222" t="str">
         <x:v>Medium</x:v>
@@ -7693,7 +7693,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I223" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Customer 360 Data Product owned by CDAO (record 218), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J223" t="str">
         <x:v>Medium</x:v>
@@ -7725,7 +7725,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I224" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Customer 360 Data Product Operational Dataset produced by Customer 360 Data Product (record 219) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J224" t="str">
         <x:v>Medium</x:v>
@@ -7757,7 +7757,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I225" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for CRM Customer Master consumes Customer 360 Data Product Operational Dataset (record 220) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J225" t="str">
         <x:v>Medium</x:v>
@@ -7789,7 +7789,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I226" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Customer 360 Data Product feeds Customer 360 Data Product Analytics Mart (record 221) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J226" t="str">
         <x:v>Medium</x:v>
@@ -7821,7 +7821,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I227" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm CRM Customer Master integrates with Identity Resolution Service (record 222) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J227" t="str">
         <x:v>Medium</x:v>
@@ -7853,7 +7853,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I228" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Identity Resolution Service depends on Customer 360 Data Product (record 223), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J228" t="str">
         <x:v>Medium</x:v>
@@ -7885,7 +7885,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I229" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Customer 360 Data Product hosted on Customer 360 Data Product Primary Northeast Data Center Hosting Segment (record 224) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J229" t="str">
         <x:v>Medium</x:v>
@@ -7917,7 +7917,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I230" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Customer 360 Data Product hosted in Primary Northeast Data Center (record 225) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J230" t="str">
         <x:v>Medium</x:v>
@@ -7949,7 +7949,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I231" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Snowflake / Databricks Cloud Data Platform target for Customer 360 Data Product Operational Dataset (record 226) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J231" t="str">
         <x:v>Medium</x:v>
@@ -7981,7 +7981,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I232" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Customer 360 Data Product governed by Enterprise Data governance council (record 227) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J232" t="str">
         <x:v>Medium</x:v>
@@ -8013,7 +8013,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I233" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Customer 360 program funded by CDAO (record 228), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J233" t="str">
         <x:v>Medium</x:v>
@@ -8045,7 +8045,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I234" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Snowflake / Databricks Cloud Data Platform replaces candidate legacy Customer 360 Data Product Operational Dataset (record 229) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J234" t="str">
         <x:v>Medium</x:v>
@@ -8077,7 +8077,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I235" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Customer 360 Data Product used by Customer 360 Data Product Analyst / Steward (record 230) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J235" t="str">
         <x:v>Medium</x:v>
@@ -8109,7 +8109,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I236" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Customer 360 Data Product Operational Dataset part of Customer 360 modernization and readiness program (record 231) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J236" t="str">
         <x:v>Medium</x:v>
@@ -8141,7 +8141,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I237" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Experian provides Customer 360 Data Product (record 232) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J237" t="str">
         <x:v>Medium</x:v>
@@ -8173,7 +8173,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I238" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Customer 360 Data Product measured by Customer 360 Data Product cycle time (record 233), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J238" t="str">
         <x:v>Medium</x:v>
@@ -8205,7 +8205,7 @@
         <x:v>HARBORTRUST-BANK-HT-CUSTOMER-360-EV01</x:v>
       </x:c>
       <x:c r="I239" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Customer 360 Data Product has risk Customer 360 Data Product data lineage and definition risk (record 234) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J239" t="str">
         <x:v>Medium</x:v>
@@ -8237,7 +8237,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I240" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Retail Banking Analytics Workflow Platform supports Retail Banking Analytics (record 235) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J240" t="str">
         <x:v>Medium</x:v>
@@ -8269,7 +8269,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I241" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Retail Banking Analytics owned by Retail Analytics Lead (record 236) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J241" t="str">
         <x:v>Medium</x:v>
@@ -8301,7 +8301,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I242" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Retail Banking Analytics Operational Dataset produced by Retail Banking Analytics Workflow Platform (record 237) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J242" t="str">
         <x:v>Medium</x:v>
@@ -8333,7 +8333,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I243" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Retail Banking Analytics Analytics Mart consumes Retail Banking Analytics Operational Dataset (record 238), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J243" t="str">
         <x:v>Medium</x:v>
@@ -8365,7 +8365,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I244" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Retail Banking Analytics Workflow Platform feeds Retail Banking Analytics Analytics Mart (record 239) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J244" t="str">
         <x:v>Medium</x:v>
@@ -8397,7 +8397,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I245" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Retail Banking Analytics Analytics Mart integrates with Retail Banking Analytics Reporting Workspace (record 240) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J245" t="str">
         <x:v>Medium</x:v>
@@ -8429,7 +8429,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I246" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Retail Banking Analytics Reporting Workspace depends on Retail Banking Analytics Workflow Platform (record 241) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J246" t="str">
         <x:v>Medium</x:v>
@@ -8461,7 +8461,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I247" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Retail Banking Analytics Workflow Platform hosted on Retail Banking Analytics Primary Northeast Data Center Hosting Segment (record 242) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J247" t="str">
         <x:v>Medium</x:v>
@@ -8493,7 +8493,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I248" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Retail Banking Analytics Workflow Platform hosted in Primary Northeast Data Center (record 243), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J248" t="str">
         <x:v>Medium</x:v>
@@ -8525,7 +8525,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I249" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Snowflake / Databricks Cloud Data Platform target for Retail Banking Analytics Operational Dataset (record 244) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J249" t="str">
         <x:v>Medium</x:v>
@@ -8557,7 +8557,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I250" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Retail Banking Analytics governed by Retail Analytics governance council (record 245) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J250" t="str">
         <x:v>Medium</x:v>
@@ -8589,7 +8589,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I251" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Retail banking analytics program funded by Retail Analytics Lead (record 246) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J251" t="str">
         <x:v>Medium</x:v>
@@ -8621,7 +8621,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I252" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Snowflake / Databricks Cloud Data Platform replaces candidate legacy Retail Banking Analytics Operational Dataset (record 247) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J252" t="str">
         <x:v>Medium</x:v>
@@ -8653,7 +8653,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I253" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Retail Banking Analytics used by Retail Banking Analytics Analyst / Steward (record 248), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J253" t="str">
         <x:v>Medium</x:v>
@@ -8685,7 +8685,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I254" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Retail Banking Analytics Operational Dataset part of Retail banking analytics modernization and readiness program (record 249) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J254" t="str">
         <x:v>Medium</x:v>
@@ -8717,7 +8717,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I255" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Snowflake provides Retail Banking Analytics Workflow Platform (record 250) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J255" t="str">
         <x:v>Medium</x:v>
@@ -8749,7 +8749,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I256" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Retail Banking Analytics measured by Retail Banking Analytics cycle time (record 251) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J256" t="str">
         <x:v>Medium</x:v>
@@ -8781,7 +8781,7 @@
         <x:v>HARBORTRUST-BANK-HT-RETAIL-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I257" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Retail Banking Analytics has risk Retail Banking Analytics data lineage and definition risk (record 252) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J257" t="str">
         <x:v>Medium</x:v>
@@ -8813,7 +8813,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I258" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Cards Portfolio Analytics Workflow Platform supports Cards Portfolio Analytics (record 253), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J258" t="str">
         <x:v>Medium</x:v>
@@ -8845,7 +8845,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I259" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Cards Portfolio Analytics owned by Cards Analytics Lead (record 254) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J259" t="str">
         <x:v>Medium</x:v>
@@ -8877,7 +8877,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I260" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Portfolio Analytics Operational Dataset produced by Cards Portfolio Analytics Workflow Platform (record 255) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J260" t="str">
         <x:v>Medium</x:v>
@@ -8909,7 +8909,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I261" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Cards Portfolio Analytics Analytics Mart consumes Cards Portfolio Analytics Operational Dataset (record 256) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J261" t="str">
         <x:v>Medium</x:v>
@@ -8941,7 +8941,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I262" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Cards Portfolio Analytics Workflow Platform feeds Cards Portfolio Analytics Analytics Mart (record 257) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J262" t="str">
         <x:v>Medium</x:v>
@@ -8973,7 +8973,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I263" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Cards Portfolio Analytics Analytics Mart integrates with Cards Portfolio Analytics Reporting Workspace (record 258), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J263" t="str">
         <x:v>Medium</x:v>
@@ -9005,7 +9005,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I264" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Cards Portfolio Analytics Reporting Workspace depends on Cards Portfolio Analytics Workflow Platform (record 259) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J264" t="str">
         <x:v>Medium</x:v>
@@ -9037,7 +9037,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I265" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Portfolio Analytics Workflow Platform hosted on Cards Portfolio Analytics Primary Northeast Data Center Hosting Segment (record 260) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J265" t="str">
         <x:v>Medium</x:v>
@@ -9069,7 +9069,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I266" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Cards Portfolio Analytics Workflow Platform hosted in Primary Northeast Data Center (record 261) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J266" t="str">
         <x:v>Medium</x:v>
@@ -9101,7 +9101,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I267" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Snowflake / Databricks Cloud Data Platform target for Cards Portfolio Analytics Operational Dataset (record 262) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J267" t="str">
         <x:v>Medium</x:v>
@@ -9133,7 +9133,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I268" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Cards Portfolio Analytics governed by Cards Analytics governance council (record 263), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J268" t="str">
         <x:v>Medium</x:v>
@@ -9165,7 +9165,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I269" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Cards analytics program funded by Cards Analytics Lead (record 264) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J269" t="str">
         <x:v>Medium</x:v>
@@ -9197,7 +9197,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I270" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Snowflake / Databricks Cloud Data Platform replaces candidate legacy Cards Portfolio Analytics Operational Dataset (record 265) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J270" t="str">
         <x:v>Medium</x:v>
@@ -9229,7 +9229,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I271" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Cards Portfolio Analytics used by Cards Portfolio Analytics Analyst / Steward (record 266) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J271" t="str">
         <x:v>Medium</x:v>
@@ -9261,7 +9261,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I272" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Cards Portfolio Analytics Operational Dataset part of Cards analytics modernization and readiness program (record 267) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J272" t="str">
         <x:v>Medium</x:v>
@@ -9293,7 +9293,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I273" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Salesforce provides Cards Portfolio Analytics Workflow Platform (record 268), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J273" t="str">
         <x:v>Medium</x:v>
@@ -9325,7 +9325,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I274" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Cards Portfolio Analytics measured by Cards Portfolio Analytics cycle time (record 269) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J274" t="str">
         <x:v>Medium</x:v>
@@ -9357,7 +9357,7 @@
         <x:v>HARBORTRUST-BANK-HT-CARDS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I275" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Portfolio Analytics has risk Cards Portfolio Analytics data lineage and definition risk (record 270) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J275" t="str">
         <x:v>Medium</x:v>
@@ -9389,7 +9389,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I276" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Payments and Settlement Analytics Workflow Platform supports Payments and Settlement Analytics (record 271) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J276" t="str">
         <x:v>Medium</x:v>
@@ -9421,7 +9421,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I277" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Payments and Settlement Analytics owned by Payments Analytics Lead (record 272) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J277" t="str">
         <x:v>Medium</x:v>
@@ -9453,7 +9453,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I278" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Payments Settlement Analytics Operational Dataset produced by Payments and Settlement Analytics Workflow Platform (record 273), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J278" t="str">
         <x:v>Medium</x:v>
@@ -9485,7 +9485,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I279" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Payments and Settlement Analytics Analytics Mart consumes Payments Settlement Analytics Operational Dataset (record 274) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J279" t="str">
         <x:v>Medium</x:v>
@@ -9517,7 +9517,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I280" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments and Settlement Analytics Workflow Platform feeds Payments Settlement Analytics Analytics Mart (record 275) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J280" t="str">
         <x:v>Medium</x:v>
@@ -9549,7 +9549,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I281" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Payments and Settlement Analytics Analytics Mart integrates with Payments and Settlement Analytics Reporting Workspace (record 276) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J281" t="str">
         <x:v>Medium</x:v>
@@ -9581,7 +9581,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I282" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Payments and Settlement Analytics Reporting Workspace depends on Payments and Settlement Analytics Workflow Platform (record 277) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J282" t="str">
         <x:v>Medium</x:v>
@@ -9613,7 +9613,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I283" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Payments and Settlement Analytics Workflow Platform hosted on Payments and Settlement Analytics Primary Northeast Data Center Hosting Segment (record 278), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J283" t="str">
         <x:v>Medium</x:v>
@@ -9645,7 +9645,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I284" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Payments and Settlement Analytics Workflow Platform hosted in Primary Northeast Data Center (record 279) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J284" t="str">
         <x:v>Medium</x:v>
@@ -9677,7 +9677,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I285" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Snowflake / Databricks Cloud Data Platform target for Payments Settlement Analytics Operational Dataset (record 280) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J285" t="str">
         <x:v>Medium</x:v>
@@ -9709,7 +9709,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I286" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Payments and Settlement Analytics governed by Payments Analytics governance council (record 281) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J286" t="str">
         <x:v>Medium</x:v>
@@ -9741,7 +9741,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I287" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Payments analytics program funded by Payments Analytics Lead (record 282) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J287" t="str">
         <x:v>Medium</x:v>
@@ -9773,7 +9773,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I288" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Snowflake / Databricks Cloud Data Platform replaces candidate legacy Payments Settlement Analytics Operational Dataset (record 283), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J288" t="str">
         <x:v>Medium</x:v>
@@ -9805,7 +9805,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I289" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Payments and Settlement Analytics used by Payments and Settlement Analytics Analyst / Steward (record 284) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J289" t="str">
         <x:v>Medium</x:v>
@@ -9837,7 +9837,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I290" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments Settlement Analytics Operational Dataset part of Payments analytics modernization and readiness program (record 285) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J290" t="str">
         <x:v>Medium</x:v>
@@ -9869,7 +9869,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I291" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Accenture Managed Services provides Payments and Settlement Analytics Workflow Platform (record 286) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J291" t="str">
         <x:v>Medium</x:v>
@@ -9901,7 +9901,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I292" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Payments and Settlement Analytics measured by Payments and Settlement Analytics cycle time (record 287) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J292" t="str">
         <x:v>Medium</x:v>
@@ -9933,7 +9933,7 @@
         <x:v>HARBORTRUST-BANK-HT-PAYMENTS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I293" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Payments and Settlement Analytics has risk Payments and Settlement Analytics data lineage and definition risk (record 288), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J293" t="str">
         <x:v>Medium</x:v>
@@ -9959,13 +9959,13 @@
         <x:v>Business Function</x:v>
       </x:c>
       <x:c r="G294" t="str">
-        <x:v>Fraud and Risk Analytics Workflow Platform supports fraud scores, alert productivity, loss trends, risk segmentation.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: High-risk digital onboarding cases require manual lookup across KYC vendor evidence, device intelligence, and core banking account history.</x:v>
       </x:c>
       <x:c r="H294" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Digital onboarding/KYC vendor report with identity verification and device-risk signals.</x:v>
       </x:c>
       <x:c r="I294" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Workflow Platform supports Fraud and Risk Analytics (record 289) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J294" t="str">
         <x:v>Medium</x:v>
@@ -9991,13 +9991,13 @@
         <x:v>Owner / Executive Role</x:v>
       </x:c>
       <x:c r="G295" t="str">
-        <x:v>Fraud Analytics Lead is accountable for Fraud and Risk Analytics evidence and readiness.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Operations leaders cannot separate true model drift from queue staffing backlogs without alert age, model version, analyst action, and loss outcome in one view.</x:v>
       </x:c>
       <x:c r="H295" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Fraud feature store design notes with feedback-loop and model governance gaps.</x:v>
       </x:c>
       <x:c r="I295" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Analytics owned by Fraud Analytics Lead (record 290) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J295" t="str">
         <x:v>Medium</x:v>
@@ -10023,13 +10023,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G296" t="str">
-        <x:v>Fraud Risk Analytics Operational Dataset is produced or sourced from Fraud and Risk Analytics Workflow Platform.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Fraud analysts triage card, ACH, wire, digital-login, and mule-account alerts in separate queues with inconsistent case priority rules.</x:v>
       </x:c>
       <x:c r="H296" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.</x:v>
       </x:c>
       <x:c r="I296" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud Risk Analytics Operational Dataset produced by Fraud and Risk Analytics Workflow Platform (record 291) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J296" t="str">
         <x:v>Medium</x:v>
@@ -10055,13 +10055,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G297" t="str">
-        <x:v>Fraud and Risk Analytics Analytics Mart consumes Fraud Risk Analytics Operational Dataset for analytics/workflow support.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: The fraud alert platform captures model score and reason codes, but downstream case outcomes are not consistently fed back to the feature store.</x:v>
       </x:c>
       <x:c r="H297" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.</x:v>
       </x:c>
       <x:c r="I297" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Analytics Mart consumes Fraud Risk Analytics Operational Dataset (record 292) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J297" t="str">
         <x:v>Medium</x:v>
@@ -10087,13 +10087,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G298" t="str">
-        <x:v>Fraud and Risk Analytics Workflow Platform feeds Fraud Risk Analytics Analytics Mart through batch/API/interface flows that require lineage validation.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: AML transaction monitoring and real-time fraud decisions use overlapping customer and counterparty fields with different freshness rules.</x:v>
       </x:c>
       <x:c r="H298" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>AML transaction monitoring source inventory and control-owner interview.</x:v>
       </x:c>
       <x:c r="I298" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Workflow Platform feeds Fraud Risk Analytics Analytics Mart (record 293) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J298" t="str">
         <x:v>Medium</x:v>
@@ -10119,13 +10119,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G299" t="str">
-        <x:v>Fraud and Risk Analytics Analytics Mart integrates with Fraud and Risk Analytics Reporting Workspace for workflow, reporting, or exception handling.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: High-risk digital onboarding cases require manual lookup across KYC vendor evidence, device intelligence, and core banking account history.</x:v>
       </x:c>
       <x:c r="H299" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Digital onboarding/KYC vendor report with identity verification and device-risk signals.</x:v>
       </x:c>
       <x:c r="I299" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Analytics Mart integrates with Fraud and Risk Analytics Reporting Workspace (record 294) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J299" t="str">
         <x:v>Medium</x:v>
@@ -10151,13 +10151,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G300" t="str">
-        <x:v>Fraud and Risk Analytics Reporting Workspace depends on Fraud and Risk Analytics Workflow Platform for source data, workflow handoff, or identity/transaction context.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Operations leaders cannot separate true model drift from queue staffing backlogs without alert age, model version, analyst action, and loss outcome in one view.</x:v>
       </x:c>
       <x:c r="H300" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Fraud feature store design notes with feedback-loop and model governance gaps.</x:v>
       </x:c>
       <x:c r="I300" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Reporting Workspace depends on Fraud and Risk Analytics Workflow Platform (record 295) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J300" t="str">
         <x:v>Medium</x:v>
@@ -10183,13 +10183,13 @@
         <x:v>Infrastructure / Platform</x:v>
       </x:c>
       <x:c r="G301" t="str">
-        <x:v>Fraud and Risk Analytics Workflow Platform is hosted on or materially depends on the Fraud and Risk Analytics hosting segment.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Fraud analysts triage card, ACH, wire, digital-login, and mule-account alerts in separate queues with inconsistent case priority rules.</x:v>
       </x:c>
       <x:c r="H301" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.</x:v>
       </x:c>
       <x:c r="I301" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Workflow Platform hosted on Fraud and Risk Analytics Primary Northeast Data Center Hosting Segment (record 296) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J301" t="str">
         <x:v>Medium</x:v>
@@ -10215,13 +10215,13 @@
         <x:v>Infrastructure / Platform</x:v>
       </x:c>
       <x:c r="G302" t="str">
-        <x:v>Fraud and Risk Analytics Workflow Platform has current or dependent hosting in Primary Northeast Data Center.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: The fraud alert platform captures model score and reason codes, but downstream case outcomes are not consistently fed back to the feature store.</x:v>
       </x:c>
       <x:c r="H302" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.</x:v>
       </x:c>
       <x:c r="I302" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Analytics Workflow Platform hosted in Primary Northeast Data Center (record 297) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J302" t="str">
         <x:v>Medium</x:v>
@@ -10247,13 +10247,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G303" t="str">
-        <x:v>Snowflake / Databricks Cloud Data Platform is the target path for governed modernization of Fraud Risk Analytics Operational Dataset.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: AML transaction monitoring and real-time fraud decisions use overlapping customer and counterparty fields with different freshness rules.</x:v>
       </x:c>
       <x:c r="H303" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>AML transaction monitoring source inventory and control-owner interview.</x:v>
       </x:c>
       <x:c r="I303" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Snowflake / Databricks Cloud Data Platform target for Fraud Risk Analytics Operational Dataset (record 298) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J303" t="str">
         <x:v>Medium</x:v>
@@ -10279,13 +10279,13 @@
         <x:v>Governance Forum</x:v>
       </x:c>
       <x:c r="G304" t="str">
-        <x:v>Risk Analytics governance council should validate evidence, exceptions, metrics, and promotion readiness.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: High-risk digital onboarding cases require manual lookup across KYC vendor evidence, device intelligence, and core banking account history.</x:v>
       </x:c>
       <x:c r="H304" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Digital onboarding/KYC vendor report with identity verification and device-risk signals.</x:v>
       </x:c>
       <x:c r="I304" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Analytics governed by Risk Analytics governance council (record 299) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J304" t="str">
         <x:v>Medium</x:v>
@@ -10311,13 +10311,13 @@
         <x:v>Owner / Executive Role</x:v>
       </x:c>
       <x:c r="G305" t="str">
-        <x:v>Fraud Analytics Lead sponsors or funds the Fraud/risk analytics modernization and readiness program.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Operations leaders cannot separate true model drift from queue staffing backlogs without alert age, model version, analyst action, and loss outcome in one view.</x:v>
       </x:c>
       <x:c r="H305" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Fraud feature store design notes with feedback-loop and model governance gaps.</x:v>
       </x:c>
       <x:c r="I305" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud/risk analytics program funded by Fraud Analytics Lead (record 300) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J305" t="str">
         <x:v>Medium</x:v>
@@ -10343,13 +10343,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G306" t="str">
-        <x:v>Fraud Risk Analytics Operational Dataset is a candidate legacy/fragmented asset to be rationalized or certified through Snowflake / Databricks Cloud Data Platform.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Fraud analysts triage card, ACH, wire, digital-login, and mule-account alerts in separate queues with inconsistent case priority rules.</x:v>
       </x:c>
       <x:c r="H306" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.</x:v>
       </x:c>
       <x:c r="I306" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Snowflake / Databricks Cloud Data Platform replaces candidate legacy Fraud Risk Analytics Operational Dataset (record 301) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J306" t="str">
         <x:v>Medium</x:v>
@@ -10375,13 +10375,13 @@
         <x:v>Workforce Role</x:v>
       </x:c>
       <x:c r="G307" t="str">
-        <x:v>Fraud and Risk Analytics analysts and stewards use this context for reporting, reconciliation, and readiness checks.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: The fraud alert platform captures model score and reason codes, but downstream case outcomes are not consistently fed back to the feature store.</x:v>
       </x:c>
       <x:c r="H307" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Fraud case management extract with confirmed fraud, false positive, recovered amount, and write-off status.</x:v>
       </x:c>
       <x:c r="I307" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Analytics used by Fraud and Risk Analytics Analyst / Steward (record 302) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J307" t="str">
         <x:v>Medium</x:v>
@@ -10407,13 +10407,13 @@
         <x:v>Program / Initiative</x:v>
       </x:c>
       <x:c r="G308" t="str">
-        <x:v>Fraud Risk Analytics Operational Dataset is in scope for Fraud/risk analytics modernization, validation, or context-readiness work.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: AML transaction monitoring and real-time fraud decisions use overlapping customer and counterparty fields with different freshness rules.</x:v>
       </x:c>
       <x:c r="H308" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>AML transaction monitoring source inventory and control-owner interview.</x:v>
       </x:c>
       <x:c r="I308" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud Risk Analytics Operational Dataset part of Fraud/risk analytics modernization and readiness program (record 303) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J308" t="str">
         <x:v>Medium</x:v>
@@ -10439,13 +10439,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G309" t="str">
-        <x:v>FIS provides, supports, or contracts around Fraud and Risk Analytics Workflow Platform.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: High-risk digital onboarding cases require manual lookup across KYC vendor evidence, device intelligence, and core banking account history.</x:v>
       </x:c>
       <x:c r="H309" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Digital onboarding/KYC vendor report with identity verification and device-risk signals.</x:v>
       </x:c>
       <x:c r="I309" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate FIS provides Fraud and Risk Analytics Workflow Platform (record 304) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J309" t="str">
         <x:v>Medium</x:v>
@@ -10471,13 +10471,13 @@
         <x:v>Metric / Outcome</x:v>
       </x:c>
       <x:c r="G310" t="str">
-        <x:v>Fraud and Risk Analytics cycle time measures Fraud and Risk Analytics performance.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Operations leaders cannot separate true model drift from queue staffing backlogs without alert age, model version, analyst action, and loss outcome in one view.</x:v>
       </x:c>
       <x:c r="H310" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Fraud feature store design notes with feedback-loop and model governance gaps.</x:v>
       </x:c>
       <x:c r="I310" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Analytics measured by Fraud and Risk Analytics cycle time (record 305) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J310" t="str">
         <x:v>Medium</x:v>
@@ -10503,13 +10503,13 @@
         <x:v>Risk / Control</x:v>
       </x:c>
       <x:c r="G311" t="str">
-        <x:v>Fraud and Risk Analytics has a known evidence/lineage risk until validation is complete.</x:v>
+        <x:v>Fraud Analyst Copilot relationship: Fraud analysts triage card, ACH, wire, digital-login, and mule-account alerts in separate queues with inconsistent case priority rules.</x:v>
       </x:c>
       <x:c r="H311" t="str">
-        <x:v>HARBORTRUST-BANK-HT-FRAUD-ANALYTICS-EV01</x:v>
+        <x:v>Fraud alert export with model score, reason code, channel, alert age, analyst action, and disposition fields.</x:v>
       </x:c>
       <x:c r="I311" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Fraud and Risk Analytics has risk Fraud and Risk Analytics data lineage and definition risk (record 306) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J311" t="str">
         <x:v>Medium</x:v>
@@ -10541,7 +10541,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I312" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Snowflake Banking Warehouse supports Cloud Data Platform (record 307) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J312" t="str">
         <x:v>Medium</x:v>
@@ -10573,7 +10573,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I313" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Cloud Data Platform owned by CDAO (record 308), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J313" t="str">
         <x:v>Medium</x:v>
@@ -10605,7 +10605,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I314" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Cloud Data Platform Operational Dataset produced by Snowflake Banking Warehouse (record 309) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J314" t="str">
         <x:v>Medium</x:v>
@@ -10637,7 +10637,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I315" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Databricks Risk Feature Workspace consumes Cloud Data Platform Operational Dataset (record 310) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J315" t="str">
         <x:v>Medium</x:v>
@@ -10669,7 +10669,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I316" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Snowflake Banking Warehouse feeds Cloud Data Platform Analytics Mart (record 311) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J316" t="str">
         <x:v>Medium</x:v>
@@ -10701,7 +10701,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I317" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Databricks Risk Feature Workspace integrates with Informatica Banking ETL (record 312) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J317" t="str">
         <x:v>Medium</x:v>
@@ -10733,7 +10733,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I318" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Informatica Banking ETL depends on Snowflake Banking Warehouse (record 313), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J318" t="str">
         <x:v>Medium</x:v>
@@ -10765,7 +10765,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I319" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Snowflake Banking Warehouse hosted on Cloud Data Platform Primary Northeast Data Center Hosting Segment (record 314) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J319" t="str">
         <x:v>Medium</x:v>
@@ -10797,7 +10797,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I320" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Snowflake Banking Warehouse hosted in Primary Northeast Data Center (record 315) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J320" t="str">
         <x:v>Medium</x:v>
@@ -10829,7 +10829,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I321" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Snowflake / Databricks Cloud Data Platform target for Cloud Data Platform Operational Dataset (record 316) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J321" t="str">
         <x:v>Medium</x:v>
@@ -10861,7 +10861,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I322" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Cloud Data Platform governed by Enterprise Data governance council (record 317) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J322" t="str">
         <x:v>Medium</x:v>
@@ -10893,7 +10893,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I323" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Enterprise data platform / cloud data foundation program funded by CDAO (record 318), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J323" t="str">
         <x:v>Medium</x:v>
@@ -10925,7 +10925,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I324" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Snowflake / Databricks Cloud Data Platform replaces candidate legacy Cloud Data Platform Operational Dataset (record 319) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J324" t="str">
         <x:v>Medium</x:v>
@@ -10957,7 +10957,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I325" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cloud Data Platform used by Cloud Data Platform Analyst / Steward (record 320) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J325" t="str">
         <x:v>Medium</x:v>
@@ -10989,7 +10989,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I326" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Cloud Data Platform Operational Dataset part of Enterprise data platform / cloud data foundation modernization and readiness program (record 321) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J326" t="str">
         <x:v>Medium</x:v>
@@ -11021,7 +11021,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I327" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Salesforce provides Snowflake Banking Warehouse (record 322) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J327" t="str">
         <x:v>Medium</x:v>
@@ -11053,7 +11053,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I328" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Cloud Data Platform measured by Cloud Data Platform cycle time (record 323), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J328" t="str">
         <x:v>Medium</x:v>
@@ -11085,7 +11085,7 @@
         <x:v>HARBORTRUST-BANK-HT-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I329" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Cloud Data Platform has risk Cloud Data Platform data lineage and definition risk (record 324) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J329" t="str">
         <x:v>Medium</x:v>
@@ -11117,7 +11117,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I330" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for IT Budget and Tower Baseline Workflow Platform supports IT Budget and Tower Baseline (record 325) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J330" t="str">
         <x:v>Medium</x:v>
@@ -11149,7 +11149,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I331" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate IT Budget and Tower Baseline owned by CIO / CFO (record 326) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J331" t="str">
         <x:v>Medium</x:v>
@@ -11181,7 +11181,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I332" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm IT Budget Tower Baseline Operational Dataset produced by IT Budget and Tower Baseline Workflow Platform (record 327) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J332" t="str">
         <x:v>Medium</x:v>
@@ -11213,7 +11213,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I333" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline Analytics Mart consumes IT Budget Tower Baseline Operational Dataset (record 328), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J333" t="str">
         <x:v>Medium</x:v>
@@ -11245,7 +11245,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I334" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile IT Budget and Tower Baseline Workflow Platform feeds IT Budget Tower Baseline Analytics Mart (record 329) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J334" t="str">
         <x:v>Medium</x:v>
@@ -11277,7 +11277,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I335" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for IT Budget and Tower Baseline Analytics Mart integrates with IT Budget and Tower Baseline Reporting Workspace (record 330) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J335" t="str">
         <x:v>Medium</x:v>
@@ -11309,7 +11309,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I336" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate IT Budget and Tower Baseline Reporting Workspace depends on IT Budget and Tower Baseline Workflow Platform (record 331) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J336" t="str">
         <x:v>Medium</x:v>
@@ -11341,7 +11341,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I337" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline Workflow Platform hosted on IT Budget and Tower Baseline Primary Northeast Data Center Hosting Segment (record 332) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J337" t="str">
         <x:v>Medium</x:v>
@@ -11373,7 +11373,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I338" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline Workflow Platform hosted in Primary Northeast Data Center (record 333), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J338" t="str">
         <x:v>Medium</x:v>
@@ -11405,7 +11405,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I339" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Snowflake / Databricks Cloud Data Platform target for IT Budget Tower Baseline Operational Dataset (record 334) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J339" t="str">
         <x:v>Medium</x:v>
@@ -11437,7 +11437,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I340" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for IT Budget and Tower Baseline governed by Technology Finance governance council (record 335) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J340" t="str">
         <x:v>Medium</x:v>
@@ -11469,7 +11469,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I341" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate IT budget and Tower spend baseline program funded by CIO / CFO (record 336) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J341" t="str">
         <x:v>Medium</x:v>
@@ -11501,7 +11501,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I342" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Snowflake / Databricks Cloud Data Platform replaces candidate legacy IT Budget Tower Baseline Operational Dataset (record 337) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J342" t="str">
         <x:v>Medium</x:v>
@@ -11533,7 +11533,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I343" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline used by IT Budget and Tower Baseline Analyst / Steward (record 338), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J343" t="str">
         <x:v>Medium</x:v>
@@ -11565,7 +11565,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I344" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile IT Budget Tower Baseline Operational Dataset part of IT budget and Tower spend baseline modernization and readiness program (record 339) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J344" t="str">
         <x:v>Medium</x:v>
@@ -11597,7 +11597,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I345" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for ServiceNow provides IT Budget and Tower Baseline Workflow Platform (record 340) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J345" t="str">
         <x:v>Medium</x:v>
@@ -11629,7 +11629,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I346" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate IT Budget and Tower Baseline measured by IT Budget and Tower Baseline cycle time (record 341) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J346" t="str">
         <x:v>Medium</x:v>
@@ -11661,7 +11661,7 @@
         <x:v>HARBORTRUST-BANK-HT-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I347" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline has risk IT Budget and Tower Baseline data lineage and definition risk (record 342) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J347" t="str">
         <x:v>Medium</x:v>
@@ -11693,7 +11693,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I348" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Vendor and Contract Optimization Workflow Platform supports Vendor and Contract Optimization (record 343), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J348" t="str">
         <x:v>Medium</x:v>
@@ -11725,7 +11725,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I349" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Vendor and Contract Optimization owned by Chief Procurement Officer (record 344) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J349" t="str">
         <x:v>Medium</x:v>
@@ -11757,7 +11757,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I350" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor Contract Optimization Operational Dataset produced by Vendor and Contract Optimization Workflow Platform (record 345) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J350" t="str">
         <x:v>Medium</x:v>
@@ -11789,7 +11789,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I351" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Vendor and Contract Optimization Analytics Mart consumes Vendor Contract Optimization Operational Dataset (record 346) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J351" t="str">
         <x:v>Medium</x:v>
@@ -11821,7 +11821,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I352" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Vendor and Contract Optimization Workflow Platform feeds Vendor Contract Optimization Analytics Mart (record 347) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J352" t="str">
         <x:v>Medium</x:v>
@@ -11853,7 +11853,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I353" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Vendor and Contract Optimization Analytics Mart integrates with Vendor and Contract Optimization Reporting Workspace (record 348), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J353" t="str">
         <x:v>Medium</x:v>
@@ -11885,7 +11885,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I354" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Vendor and Contract Optimization Reporting Workspace depends on Vendor and Contract Optimization Workflow Platform (record 349) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J354" t="str">
         <x:v>Medium</x:v>
@@ -11917,7 +11917,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I355" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization Workflow Platform hosted on Vendor and Contract Optimization Primary Northeast Data Center Hosting Segment (record 350) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J355" t="str">
         <x:v>Medium</x:v>
@@ -11949,7 +11949,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I356" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Vendor and Contract Optimization Workflow Platform hosted in Primary Northeast Data Center (record 351) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J356" t="str">
         <x:v>Medium</x:v>
@@ -11981,7 +11981,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I357" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Snowflake / Databricks Cloud Data Platform target for Vendor Contract Optimization Operational Dataset (record 352) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J357" t="str">
         <x:v>Medium</x:v>
@@ -12013,7 +12013,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I358" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Vendor and Contract Optimization governed by Procurement and Vendor Management governance council (record 353), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J358" t="str">
         <x:v>Medium</x:v>
@@ -12045,7 +12045,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I359" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Vendor / contract / sourcing context program funded by Chief Procurement Officer (record 354) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J359" t="str">
         <x:v>Medium</x:v>
@@ -12077,7 +12077,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I360" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Snowflake / Databricks Cloud Data Platform replaces candidate legacy Vendor Contract Optimization Operational Dataset (record 355) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J360" t="str">
         <x:v>Medium</x:v>
@@ -12109,7 +12109,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I361" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Vendor and Contract Optimization used by Vendor and Contract Optimization Analyst / Steward (record 356) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J361" t="str">
         <x:v>Medium</x:v>
@@ -12141,7 +12141,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I362" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Vendor Contract Optimization Operational Dataset part of Vendor / contract / sourcing context modernization and readiness program (record 357) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J362" t="str">
         <x:v>Medium</x:v>
@@ -12173,7 +12173,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I363" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for FIS provides Vendor and Contract Optimization Workflow Platform (record 358), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J363" t="str">
         <x:v>Medium</x:v>
@@ -12205,7 +12205,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I364" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Vendor and Contract Optimization measured by Vendor and Contract Optimization cycle time (record 359) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J364" t="str">
         <x:v>Medium</x:v>
@@ -12237,7 +12237,7 @@
         <x:v>HARBORTRUST-BANK-HT-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I365" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization has risk Vendor and Contract Optimization data lineage and definition risk (record 360) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J365" t="str">
         <x:v>Medium</x:v>
@@ -12269,7 +12269,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I366" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate ServiceNow CMDB supports Infrastructure and CMDB (record 361) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J366" t="str">
         <x:v>Medium</x:v>
@@ -12301,7 +12301,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I367" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Infrastructure and CMDB owned by CTO (record 362) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J367" t="str">
         <x:v>Medium</x:v>
@@ -12333,7 +12333,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I368" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Infrastructure CMDB Operational Dataset produced by ServiceNow CMDB (record 363), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J368" t="str">
         <x:v>Medium</x:v>
@@ -12365,7 +12365,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I369" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile IBM z/OS Mainframe Cluster consumes Infrastructure CMDB Operational Dataset (record 364) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J369" t="str">
         <x:v>Medium</x:v>
@@ -12397,7 +12397,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I370" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for ServiceNow CMDB feeds Infrastructure CMDB Analytics Mart (record 365) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J370" t="str">
         <x:v>Medium</x:v>
@@ -12429,7 +12429,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I371" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate IBM z/OS Mainframe Cluster integrates with Azure Banking Landing Zone (record 366) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J371" t="str">
         <x:v>Medium</x:v>
@@ -12461,7 +12461,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I372" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Azure Banking Landing Zone depends on ServiceNow CMDB (record 367) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J372" t="str">
         <x:v>Medium</x:v>
@@ -12493,7 +12493,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I373" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for ServiceNow CMDB hosted on Infrastructure and CMDB Primary Northeast Data Center Hosting Segment (record 368), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J373" t="str">
         <x:v>Medium</x:v>
@@ -12525,7 +12525,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I374" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile ServiceNow CMDB hosted in Primary Northeast Data Center (record 369) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J374" t="str">
         <x:v>Medium</x:v>
@@ -12557,7 +12557,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I375" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Snowflake / Databricks Cloud Data Platform target for Infrastructure CMDB Operational Dataset (record 370) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J375" t="str">
         <x:v>Medium</x:v>
@@ -12589,7 +12589,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I376" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Infrastructure and CMDB governed by Technology Operations governance council (record 371) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J376" t="str">
         <x:v>Medium</x:v>
@@ -12621,7 +12621,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I377" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm CMDB / infrastructure / cloud inventory context program funded by CTO (record 372) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J377" t="str">
         <x:v>Medium</x:v>
@@ -12653,7 +12653,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I378" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Snowflake / Databricks Cloud Data Platform replaces candidate legacy Infrastructure CMDB Operational Dataset (record 373), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J378" t="str">
         <x:v>Medium</x:v>
@@ -12685,7 +12685,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I379" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Infrastructure and CMDB used by Infrastructure and CMDB Analyst / Steward (record 374) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J379" t="str">
         <x:v>Medium</x:v>
@@ -12717,7 +12717,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I380" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Infrastructure CMDB Operational Dataset part of CMDB / infrastructure / cloud inventory context modernization and readiness program (record 375) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J380" t="str">
         <x:v>Medium</x:v>
@@ -12749,7 +12749,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I381" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate TransUnion provides ServiceNow CMDB (record 376) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J381" t="str">
         <x:v>Medium</x:v>
@@ -12781,7 +12781,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I382" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Infrastructure and CMDB measured by Infrastructure and CMDB cycle time (record 377) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J382" t="str">
         <x:v>Medium</x:v>
@@ -12813,7 +12813,7 @@
         <x:v>HARBORTRUST-BANK-HT-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I383" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Infrastructure and CMDB has risk Infrastructure and CMDB data lineage and definition risk (record 378), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J383" t="str">
         <x:v>Medium</x:v>
@@ -12845,7 +12845,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I384" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile ServiceNow ITSM supports Incident Problem Change Operations (record 379) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J384" t="str">
         <x:v>Medium</x:v>
@@ -12877,7 +12877,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I385" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident Problem Change Operations owned by VP IT Operations (record 380) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J385" t="str">
         <x:v>Medium</x:v>
@@ -12909,7 +12909,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I386" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Incident Problem Change Operations Operational Dataset produced by ServiceNow ITSM (record 381) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J386" t="str">
         <x:v>Medium</x:v>
@@ -12941,7 +12941,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I387" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Splunk Observability consumes Incident Problem Change Operations Operational Dataset (record 382) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J387" t="str">
         <x:v>Medium</x:v>
@@ -12973,7 +12973,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I388" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for ServiceNow ITSM feeds Incident Problem Change Operations Analytics Mart (record 383), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J388" t="str">
         <x:v>Medium</x:v>
@@ -13005,7 +13005,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I389" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Splunk Observability integrates with PagerDuty Incident Response (record 384) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J389" t="str">
         <x:v>Medium</x:v>
@@ -13037,7 +13037,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I390" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for PagerDuty Incident Response depends on ServiceNow ITSM (record 385) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J390" t="str">
         <x:v>Medium</x:v>
@@ -13069,7 +13069,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I391" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate ServiceNow ITSM hosted on Incident Problem Change Operations Primary Northeast Data Center Hosting Segment (record 386) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J391" t="str">
         <x:v>Medium</x:v>
@@ -13101,7 +13101,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I392" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm ServiceNow ITSM hosted in Primary Northeast Data Center (record 387) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J392" t="str">
         <x:v>Medium</x:v>
@@ -13133,7 +13133,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I393" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Snowflake / Databricks Cloud Data Platform target for Incident Problem Change Operations Operational Dataset (record 388), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J393" t="str">
         <x:v>Medium</x:v>
@@ -13165,7 +13165,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I394" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Incident Problem Change Operations governed by Technology Operations governance council (record 389) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J394" t="str">
         <x:v>Medium</x:v>
@@ -13197,7 +13197,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I395" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident / problem / change operational health context program funded by VP IT Operations (record 390) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J395" t="str">
         <x:v>Medium</x:v>
@@ -13229,7 +13229,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I396" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Snowflake / Databricks Cloud Data Platform replaces candidate legacy Incident Problem Change Operations Operational Dataset (record 391) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J396" t="str">
         <x:v>Medium</x:v>
@@ -13261,7 +13261,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I397" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Incident Problem Change Operations used by Incident Problem Change Operations Analyst / Steward (record 392) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J397" t="str">
         <x:v>Medium</x:v>
@@ -13293,7 +13293,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I398" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Incident Problem Change Operations Operational Dataset part of Incident / problem / change operational health context modernization and readiness program (record 393), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J398" t="str">
         <x:v>Medium</x:v>
@@ -13325,7 +13325,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I399" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile TransUnion provides ServiceNow ITSM (record 394) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J399" t="str">
         <x:v>Medium</x:v>
@@ -13357,7 +13357,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I400" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident Problem Change Operations measured by Incident Problem Change Operations cycle time (record 395) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J400" t="str">
         <x:v>Medium</x:v>
@@ -13389,7 +13389,7 @@
         <x:v>HARBORTRUST-BANK-HT-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I401" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Incident Problem Change Operations has risk Incident Problem Change Operations data lineage and definition risk (record 396) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J401" t="str">
         <x:v>Medium</x:v>
@@ -13416,7 +13416,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b179551f09546d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4efbbef38384492b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13491,7 +13491,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb16a1b09da04862"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2fefea44a794ffe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13785,7 +13785,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8082339d04934e02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7016f4c959f4a0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13863,7 +13863,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf3b2eb76ea24769"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d2b8797d00b45fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13973,7 +13973,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a642a94235b4fd6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb1498b532b54460"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14169,7 +14169,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a8103d2bc8d40dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27c5026cff234caf"/>
   </x:tableParts>
 </x:worksheet>
 </file>